--- a/yscap-repo-root_8/web/tools/templates/portfolio-tracker.xlsx
+++ b/yscap-repo-root_8/web/tools/templates/portfolio-tracker.xlsx
@@ -9916,8 +9916,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010013FC264900052B4E8B7EFCB5708AF87F" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a04d37ce0c42a9d4ad4e25919536400">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8e991a0-14da-48f8-b377-886d3df09443" xmlns:ns3="d7eac4ec-cfe6-44c1-8384-f889af4f723e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="17f759dd88c0267f8c2669011ec5131e" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010013FC264900052B4E8B7EFCB5708AF87F" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64d2cbc56a22ac5cd338f08e0e4464ab">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8e991a0-14da-48f8-b377-886d3df09443" xmlns:ns3="d7eac4ec-cfe6-44c1-8384-f889af4f723e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a18193c64b0e2170cc0565e8c23d6ba" ns2:_="" ns3:_="">
     <xsd:import namespace="e8e991a0-14da-48f8-b377-886d3df09443"/>
     <xsd:import namespace="d7eac4ec-cfe6-44c1-8384-f889af4f723e"/>
     <xsd:element name="properties">
@@ -9938,6 +9938,7 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -10005,6 +10006,11 @@
     <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -10142,22 +10148,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69102E46-205E-437B-B85B-AA967F24E9D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e8e991a0-14da-48f8-b377-886d3df09443"/>
-    <ds:schemaRef ds:uri="d7eac4ec-cfe6-44c1-8384-f889af4f723e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC071867-7FAB-48AD-AD96-7F2054E0BFF2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/yscap-repo-root_8/web/tools/templates/portfolio-tracker.xlsx
+++ b/yscap-repo-root_8/web/tools/templates/portfolio-tracker.xlsx
@@ -9916,8 +9916,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010013FC264900052B4E8B7EFCB5708AF87F" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a04d37ce0c42a9d4ad4e25919536400">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8e991a0-14da-48f8-b377-886d3df09443" xmlns:ns3="d7eac4ec-cfe6-44c1-8384-f889af4f723e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="17f759dd88c0267f8c2669011ec5131e" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010013FC264900052B4E8B7EFCB5708AF87F" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64d2cbc56a22ac5cd338f08e0e4464ab">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8e991a0-14da-48f8-b377-886d3df09443" xmlns:ns3="d7eac4ec-cfe6-44c1-8384-f889af4f723e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a18193c64b0e2170cc0565e8c23d6ba" ns2:_="" ns3:_="">
     <xsd:import namespace="e8e991a0-14da-48f8-b377-886d3df09443"/>
     <xsd:import namespace="d7eac4ec-cfe6-44c1-8384-f889af4f723e"/>
     <xsd:element name="properties">
@@ -9938,6 +9938,7 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -10005,6 +10006,11 @@
     <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -10142,22 +10148,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69102E46-205E-437B-B85B-AA967F24E9D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e8e991a0-14da-48f8-b377-886d3df09443"/>
-    <ds:schemaRef ds:uri="d7eac4ec-cfe6-44c1-8384-f889af4f723e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{760F503A-3AEC-4D85-8D4C-F462191A1C38}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
